--- a/tools/reports/nav-unmigrated.xlsx
+++ b/tools/reports/nav-unmigrated.xlsx
@@ -5,14 +5,15 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Unmigrated nav links" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Local links without page" state="visible" r:id="rId5"/>
+    <sheet sheetId="2" name="All nav links" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="About" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="504">
   <si>
     <t>Nav area</t>
   </si>
@@ -26,12 +27,15 @@
     <t>Current target URL</t>
   </si>
   <si>
-    <t>HTTP status on source</t>
+    <t>HTTP status (final)</t>
   </si>
   <si>
     <t>Final URL after redirects</t>
   </si>
   <si>
+    <t>Page exists on www.bmw.de</t>
+  </si>
+  <si>
     <t>Under www.bmw.de/de/ (in migration scope)</t>
   </si>
   <si>
@@ -50,6 +54,9 @@
     <t>https://www.bmw.de/de-de/sl/neuwagensuche/results?filters=%257B%2522IS_INSTALLMENT%2522%253Atrue%252C%2522PRODUCT_CATEGORY_TYPE%2522%253A%255B%2522LEASE%2522%252C%2522LOAN%2522%255D%252C%2522PURCHASE_ONLINE%2522%253A%255Btrue%255D%257D</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>no (www.bmw.de, outside /de/)</t>
   </si>
   <si>
@@ -65,10 +72,13 @@
     <t>https://bmw-rent.de/b2c/select-station-and-time</t>
   </si>
   <si>
+    <t>n/a (other domain)</t>
+  </si>
+  <si>
     <t>no (other domain)</t>
   </si>
   <si>
-    <t>external BMW domain (bmw-rent.de)</t>
+    <t>other domain (bmw-rent.de)</t>
   </si>
   <si>
     <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Vergleichen</t>
@@ -80,10 +90,7 @@
     <t>https://www.bmw.de/de/bmw-modelle-vergleichen.html/content.q</t>
   </si>
   <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>compare app deep link (content.q); migrated page /de/bmw-modelle-vergleichen exists</t>
+    <t>compare app deep link; migrated page /de/bmw-modelle-vergleichen exists</t>
   </si>
   <si>
     <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Online-Kaufberatung</t>
@@ -95,7 +102,7 @@
     <t>https://www.bmw-welt.com/de/freude-am-fahren/fahrzeugberatung.html</t>
   </si>
   <si>
-    <t>external BMW domain (www.bmw-welt.com)</t>
+    <t>other domain (www.bmw-welt.com)</t>
   </si>
   <si>
     <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Probefahrt buchen</t>
@@ -170,7 +177,7 @@
     <t>https://www.bmw.de/faas/form/de-de/bmw/rfo/angebotsanfrage.html</t>
   </si>
   <si>
-    <t>non-page URL on www.bmw.de</t>
+    <t>app: forms</t>
   </si>
   <si>
     <t>Kunden &gt; Fahrzeugservice &amp; Verträge &gt; Verträge &amp; Zahlungen</t>
@@ -182,7 +189,7 @@
     <t>https://meinfs.bmw.de/de/home.html</t>
   </si>
   <si>
-    <t>external BMW domain (meinfs.bmw.de)</t>
+    <t>other domain (meinfs.bmw.de)</t>
   </si>
   <si>
     <t>Kunden &gt; Fahrzeugservice &amp; Verträge &gt; Inzahlungnahme &amp; Fahrzeug verkaufen</t>
@@ -212,7 +219,7 @@
     <t>https://www.bmwgroup.com/de.html</t>
   </si>
   <si>
-    <t>external BMW domain (www.bmwgroup.com)</t>
+    <t>other domain (www.bmwgroup.com)</t>
   </si>
   <si>
     <t>Marke &gt; Marke &amp; Unternehmen &gt; BMW Welt &amp; Werksführung</t>
@@ -233,7 +240,7 @@
     <t>https://www.bmwgroup.jobs/de/de.html</t>
   </si>
   <si>
-    <t>external BMW domain (www.bmwgroup.jobs)</t>
+    <t>other domain (www.bmwgroup.jobs)</t>
   </si>
   <si>
     <t>Marke &gt; Marke &amp; Unternehmen &gt; Nachhaltigkeit</t>
@@ -263,7 +270,7 @@
     <t>https://www.bmw-m.com/de/fastlane/motorsport/motorsport.html</t>
   </si>
   <si>
-    <t>external BMW domain (www.bmw-m.com)</t>
+    <t>other domain (www.bmw-m.com)</t>
   </si>
   <si>
     <t>Marke &gt; Technologie &amp; Innovation &gt; Personal Pilot L3</t>
@@ -278,13 +285,13 @@
     <t>header</t>
   </si>
   <si>
-    <t>:shopping_cart: Warenkorb</t>
+    <t>Warenkorb</t>
   </si>
   <si>
     <t>https://www.bmw.de/de/shop/ls/cart/digital-services</t>
   </si>
   <si>
-    <t>:heart: Wunschliste</t>
+    <t>Wunschliste</t>
   </si>
   <si>
     <t>https://www.bmw.de/de/shop/ls/wishlist</t>
@@ -293,13 +300,13 @@
     <t>https://www.bmw.de/de/shop/ls/wishlist/login</t>
   </si>
   <si>
-    <t>:location_pin: Händlersuche</t>
+    <t>Händlersuche</t>
   </si>
   <si>
     <t>https://www.bmw.de/dlo/de-de/bmw/dealer-locator.html</t>
   </si>
   <si>
-    <t>app: dealer locator (DLO); migrated equivalent is /de/fastlane/dealer-locator</t>
+    <t>app: dealer locator (DLO); migrated equivalent /de/fastlane/dealer-locator</t>
   </si>
   <si>
     <t>Willkommen bei My BMW. &gt; Anmelden</t>
@@ -311,6 +318,9 @@
     <t>https://www.bmw.de/de-de/login/bmw/mylogin</t>
   </si>
   <si>
+    <t>no (400)</t>
+  </si>
+  <si>
     <t>Willkommen bei My BMW. &gt; Registrieren</t>
   </si>
   <si>
@@ -350,9 +360,6 @@
     <t>https://www.bmw.de/faas/form/de-de/bmw/rfo/angebotsanfrage.html?midstatic=4g0agj01ba51d05hb9aas</t>
   </si>
   <si>
-    <t>app: forms (FaaS)</t>
-  </si>
-  <si>
     <t>BMW erleben &gt; BMW Karriere</t>
   </si>
   <si>
@@ -380,7 +387,7 @@
     <t>https://open.bmwgroup.com/bmw.html</t>
   </si>
   <si>
-    <t>external BMW domain (open.bmwgroup.com)</t>
+    <t>other domain (open.bmwgroup.com)</t>
   </si>
   <si>
     <t>Service- &amp; Dienstleistungen &gt; BMW Drivers Guide App</t>
@@ -440,9 +447,6 @@
     <t>Auswählen &amp; Kaufen &gt; Wunschliste</t>
   </si>
   <si>
-    <t>Wunschliste</t>
-  </si>
-  <si>
     <t>Auswählen &amp; Kaufen &gt; ConnectedDrive Store</t>
   </si>
   <si>
@@ -488,10 +492,229 @@
     <t>https://ipm.bmw.com/lean-ipm/digitalhub_dcdc/rfcn_bmw_de</t>
   </si>
   <si>
-    <t>external BMW domain (ipm.bmw.com)</t>
-  </si>
-  <si>
-    <t>Local target</t>
+    <t>other domain (ipm.bmw.com)</t>
+  </si>
+  <si>
+    <t>Authored href</t>
+  </si>
+  <si>
+    <t>Resolved URL</t>
+  </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Redirects</t>
+  </si>
+  <si>
+    <t>Final HTTP status</t>
+  </si>
+  <si>
+    <t>Final target</t>
+  </si>
+  <si>
+    <t>Dead (local: 404/error only)</t>
+  </si>
+  <si>
+    <t>Skip to main content</t>
+  </si>
+  <si>
+    <t>#main</t>
+  </si>
+  <si>
+    <t>in-page / non-http</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>BMW Logo</t>
+  </si>
+  <si>
+    <t>/de/home</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/home</t>
+  </si>
+  <si>
+    <t>local (migrated page)</t>
+  </si>
+  <si>
+    <t>Modelle</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; Alle Modelle</t>
+  </si>
+  <si>
+    <t>Alle Modelle</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; Konfigurator</t>
+  </si>
+  <si>
+    <t>Konfigurator</t>
+  </si>
+  <si>
+    <t>/de/konfigurator</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/konfigurator</t>
+  </si>
+  <si>
+    <t>BMW domain</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; Gebrauchtwagen</t>
+  </si>
+  <si>
+    <t>Gebrauchtwagen</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/bmw-gebrauchte</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/bmw-gebrauchte</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; Junge Gebrauchte - Jahreswagen</t>
+  </si>
+  <si>
+    <t>Junge Gebrauchte - Jahreswagen</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/bmw-gebrauchte/junge-gebrauchte</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/bmw-gebrauchte/junge-gebrauchte</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; BMW individualisieren</t>
+  </si>
+  <si>
+    <t>BMW individualisieren</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/bmw-individual</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/bmw-individual</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Fahrzeuge &amp; Konfigurieren &gt; Exklusive Modelle</t>
+  </si>
+  <si>
+    <t>Exklusive Modelle</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/die-exklusiven-bmw-automobile</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/die-exklusiven-bmw-automobile</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Geschäftskunden</t>
+  </si>
+  <si>
+    <t>Geschäftskunden</t>
+  </si>
+  <si>
+    <t>/de/campaigns/bmw-fuer-geschaeftskunden</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/campaigns/bmw-fuer-geschaeftskunden</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Großkunden</t>
+  </si>
+  <si>
+    <t>Großkunden</t>
+  </si>
+  <si>
+    <t>/de/topics/faszination-bmw/grosskunden-behoerden/corporate-sales</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/faszination-bmw/grosskunden-behoerden/corporate-sales</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Beratung &amp; Geschäftskunden &gt; Behörden- und Sonderschutzfahrzeuge</t>
+  </si>
+  <si>
+    <t>Behörden- und Sonderschutzfahrzeuge</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/bmw-special-sales</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/bmw-special-sales</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Digitale Dienste &amp; Zubehör &gt; Original BMW Zubehör</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/teile-und-zubehoer/bmw-zubehoer-hub</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/teile-und-zubehoer/bmw-zubehoer-hub</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Digitale Dienste &amp; Zubehör &gt; Original BMW Teile</t>
+  </si>
+  <si>
+    <t>Original BMW Teile</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/teile-und-zubehoer/original-bmw-teile</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/teile-und-zubehoer/original-bmw-teile</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Digitale Dienste &amp; Zubehör &gt; BMW Security</t>
+  </si>
+  <si>
+    <t>BMW Security</t>
+  </si>
+  <si>
+    <t>/de/topics/service-zubehoer/bmw-security</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/service-zubehoer/bmw-security</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Services &amp; Finanzierungen &gt; Finanzierung &amp; Leasing</t>
+  </si>
+  <si>
+    <t>Finanzierung &amp; Leasing</t>
+  </si>
+  <si>
+    <t>/de/topics/service-zubehoer/financial-services/bmw-financial-services</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/service-zubehoer/financial-services/bmw-financial-services</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Services &amp; Finanzierungen &gt; Leasingbeispiel Privatkunden</t>
+  </si>
+  <si>
+    <t>Leasingbeispiel Privatkunden</t>
+  </si>
+  <si>
+    <t>/de/shop-online/bmw-offers</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/shop-online/bmw-offers</t>
   </si>
   <si>
     <t>Kaufen &gt; Services &amp; Finanzierungen &gt; Leasingbeispiel Gewerbekunden</t>
@@ -503,6 +726,75 @@
     <t>/de/shop-online/bmw-gewerbeangebote</t>
   </si>
   <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/shop-online/bmw-gewerbeangebote</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de-de/shop-online/bmw-business-offers</t>
+  </si>
+  <si>
+    <t>Kaufen &gt; Services &amp; Finanzierungen &gt; BMW Service &amp; Pakete</t>
+  </si>
+  <si>
+    <t>BMW Service &amp; Pakete</t>
+  </si>
+  <si>
+    <t>/de/bmw-service-hub</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/bmw-service-hub</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Elektroautos</t>
+  </si>
+  <si>
+    <t>Elektroautos</t>
+  </si>
+  <si>
+    <t>/de/elektroauto</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Gebrauchte Elektroautos</t>
+  </si>
+  <si>
+    <t>Gebrauchte Elektroautos</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/gebrauchte-elektroautos</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/gebrauchte-elektroautos</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Vorteile von Elektroautos</t>
+  </si>
+  <si>
+    <t>Vorteile von Elektroautos</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/elektroautos-vorteile</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/elektroautos-vorteile</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Kosten eines Elektroautos</t>
+  </si>
+  <si>
+    <t>Kosten eines Elektroautos</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/elektroauto-kosten</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/elektroauto-kosten</t>
+  </si>
+  <si>
     <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Förderungen Elektroautos Privatkunden</t>
   </si>
   <si>
@@ -512,16 +804,727 @@
     <t>/de/elektroauto/foerderungen_privatkunden</t>
   </si>
   <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/foerderungen_privatkunden</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/foerderungen-privatkunden</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Förderungen Elektroautos Gewerbekunden</t>
+  </si>
+  <si>
+    <t>Förderungen Elektroautos Gewerbekunden</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/foerderungen</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/foerderungen</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Fahrzeuge &amp; Kauf &gt; Plug-in-Hybrid</t>
+  </si>
+  <si>
+    <t>Plug-in-Hybrid</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/plug-in-hybrid</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/plug-in-hybrid</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Laden &amp; Reichweite &gt; Zuhause laden</t>
+  </si>
+  <si>
+    <t>Zuhause laden</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/home-charging</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/home-charging</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Laden &amp; Reichweite &gt; Öffentliches laden</t>
+  </si>
+  <si>
+    <t>Öffentliches laden</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/public-charging</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/public-charging</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Laden &amp; Reichweite &gt; E-Auto-Batterie &amp; E‑Motor</t>
+  </si>
+  <si>
+    <t>E-Auto-Batterie &amp; E‑Motor</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/batterie-technologie</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/batterie-technologie</t>
+  </si>
+  <si>
+    <t>E-Mobilität &gt; Laden &amp; Reichweite &gt; Reichweite von Elektroautos</t>
+  </si>
+  <si>
+    <t>Reichweite von Elektroautos</t>
+  </si>
+  <si>
+    <t>/de/elektroauto/elektroauto-reichweite</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/elektroauto/elektroauto-reichweite</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Fahrzeugservice &amp; Verträge &gt; Versicherungen– Schutz &amp; Schadenservice</t>
+  </si>
+  <si>
+    <t>Versicherungen– Schutz &amp; Schadenservice</t>
+  </si>
+  <si>
+    <t>/de/topics/service-zubehoer/financial-services/bmw-financial-services#BMW_Versicherungen</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/service-zubehoer/financial-services/bmw-financial-services#BMW_Versicherungen</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Fahrzeugservice &amp; Verträge &gt; Gewährleistung &amp; Garantien</t>
+  </si>
+  <si>
+    <t>Gewährleistung &amp; Garantien</t>
+  </si>
+  <si>
+    <t>/de/topics/neuwagen/gewaehrleistung</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/neuwagen/gewaehrleistung</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Fahrzeugservice &amp; Verträge &gt; Rückrufe &amp; Technische Updates</t>
+  </si>
+  <si>
+    <t>Rückrufe &amp; Technische Updates</t>
+  </si>
+  <si>
+    <t>/de/topics/service-zubehoer/bmw-service/rueckrufe</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/topics/service-zubehoer/bmw-service/rueckrufe</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Service &amp; Hilfe &gt; Alle Services</t>
+  </si>
+  <si>
+    <t>Alle Services</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Service &amp; Hilfe &gt; Hilfe &amp; Kontakt</t>
+  </si>
+  <si>
+    <t>Hilfe &amp; Kontakt</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/kundenbetreuung</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/kundenbetreuung</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Service &amp; Hilfe &gt; Betriebsanleitungen</t>
+  </si>
+  <si>
+    <t>Betriebsanleitungen</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Service &amp; Hilfe &gt; Unfall &amp; Pannenhilfe</t>
+  </si>
+  <si>
+    <t>Unfall &amp; Pannenhilfe</t>
+  </si>
+  <si>
+    <t>/de/bmw-service-hub#unfall-und-pannenhilfe</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/bmw-service-hub#unfall-und-pannenhilfe</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Service &amp; Hilfe &gt; BMW Partner finden</t>
+  </si>
+  <si>
+    <t>/de/fastlane/dealer-locator</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/fastlane/dealer-locator</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Digitale Dienste &amp; Apps &gt; My BMW App - Vernetztes Fahrzeug</t>
+  </si>
+  <si>
+    <t>My BMW App - Vernetztes Fahrzeug</t>
+  </si>
+  <si>
+    <t>/de/my-bmw-app/my-bmw-app</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/my-bmw-app/my-bmw-app</t>
+  </si>
+  <si>
+    <t>Kunden &gt; Digitale Dienste &amp; Apps &gt; BMW ConnectedDrive - Digitale Dienste</t>
+  </si>
+  <si>
+    <t>BMW ConnectedDrive - Digitale Dienste</t>
+  </si>
+  <si>
+    <t>/de/digital-services/bmw-connecteddrive</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/digital-services/bmw-connecteddrive</t>
+  </si>
+  <si>
+    <t>Marke &gt; Erlebnisse &amp; Veranstaltungen &gt; Ticketshop</t>
+  </si>
+  <si>
+    <t>Ticketshop</t>
+  </si>
+  <si>
+    <t>https://ticketorganizer.eu/organizer/bmw-ticketshop?lang=de&amp;_pes=1</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>Marke &gt; Erlebnisse &amp; Veranstaltungen &gt; Sport &amp; Kultur</t>
+  </si>
+  <si>
+    <t>Sport &amp; Kultur</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/sport-und-events/sport-und-kultur</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/sport-und-events/sport-und-kultur</t>
+  </si>
+  <si>
+    <t>Marke &gt; Erlebnisse &amp; Veranstaltungen &gt; Gewinnspiele</t>
+  </si>
+  <si>
+    <t>Gewinnspiele</t>
+  </si>
+  <si>
+    <t>/de/landingpage/bmw-fahrfreude-gewinnen</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/landingpage/bmw-fahrfreude-gewinnen</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; Elektromobilität</t>
+  </si>
+  <si>
+    <t>Elektromobilität</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; Speedtop</t>
+  </si>
+  <si>
+    <t>Speedtop</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/concept-cars/bmw-speedtop</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/concept-cars/bmw-speedtop</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; Heart of Joy - Zentrale Fahrdynamik</t>
+  </si>
+  <si>
+    <t>Heart of Joy - Zentrale Fahrdynamik</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/technology-and-innovation/bmw-heart-of-joy</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/technology-and-innovation/bmw-heart-of-joy</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; iDrive - Fahrzeuginterface</t>
+  </si>
+  <si>
+    <t>iDrive - Fahrzeuginterface</t>
+  </si>
+  <si>
+    <t>/de/digital-services/bmw-idrive</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/digital-services/bmw-idrive</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; HVO100</t>
+  </si>
+  <si>
+    <t>HVO100</t>
+  </si>
+  <si>
+    <t>/de/campaigns/hvo100-erneuerbarer-diesel</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/campaigns/hvo100-erneuerbarer-diesel</t>
+  </si>
+  <si>
+    <t>Marke &gt; Technologie &amp; Innovation &gt; Pkw-EnVKV</t>
+  </si>
+  <si>
+    <t>Pkw-EnVKV</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/bmw-efficientdynamics/pkw-envkv</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/bmw-efficientdynamics/pkw-envkv</t>
+  </si>
+  <si>
+    <t>Marke &gt; Vision BMW ALPINA</t>
+  </si>
+  <si>
+    <t>Vision BMW ALPINA</t>
+  </si>
+  <si>
+    <t>/de/bmw-alpina</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/bmw-alpina</t>
+  </si>
+  <si>
+    <t>Jetzt entdecken</t>
+  </si>
+  <si>
+    <t>Kontakt &gt; Hilfe &amp; Kontakt</t>
+  </si>
+  <si>
+    <t>https://www.bmw.de/de/s/?language=de#_blank</t>
+  </si>
+  <si>
+    <t>Kontakt &gt; Unfall- und Pannenhilfe</t>
+  </si>
+  <si>
+    <t>Unfall- und Pannenhilfe</t>
+  </si>
+  <si>
+    <t>/de/bmw-service-hub/bmw-service/unfall-pannenhilfe</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/bmw-service-hub/bmw-service/unfall-pannenhilfe</t>
+  </si>
+  <si>
+    <t>BMW erleben &gt; BMW.com</t>
+  </si>
+  <si>
+    <t>BMW.com</t>
+  </si>
+  <si>
+    <t>https://open.bmwgroup.com/bmw.html#_blank</t>
+  </si>
+  <si>
+    <t>Service- &amp; Dienstleistungen &gt; ConnectedDrive Services</t>
+  </si>
+  <si>
+    <t>ConnectedDrive Services</t>
+  </si>
+  <si>
+    <t>Service- &amp; Dienstleistungen &gt; Gewährleistung und Garantien</t>
+  </si>
+  <si>
+    <t>Gewährleistung und Garantien</t>
+  </si>
+  <si>
+    <t>Service- &amp; Dienstleistungen &gt; Remote Software Upgrades</t>
+  </si>
+  <si>
+    <t>Remote Software Upgrades</t>
+  </si>
+  <si>
+    <t>https://www.bmw.de/content/dam/bmw/marketDE/bmw_de/BMW_Recycling_und_Ruecknahmestellen_Uebersicht_260212.pdf.asset.1771311194085.pdf#_blank</t>
+  </si>
+  <si>
+    <t>Auswählen &amp; Kaufen &gt; Konfigurator</t>
+  </si>
+  <si>
+    <t>Auswählen &amp; Kaufen &gt; BMW Online Stores</t>
+  </si>
+  <si>
+    <t>BMW Online Stores</t>
+  </si>
+  <si>
+    <t>/de/landingpage/shops</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/landingpage/shops</t>
+  </si>
+  <si>
+    <t>https://meinfs.bmw.de/de/home.html#_blank</t>
+  </si>
+  <si>
+    <t>Auswählen &amp; Kaufen &gt; Finanzierung und Leasing</t>
+  </si>
+  <si>
+    <t>Finanzierung und Leasing</t>
+  </si>
+  <si>
+    <t>Auswählen &amp; Kaufen &gt; Leasingbeispiele für Privatkunden</t>
+  </si>
+  <si>
+    <t>Leasingbeispiele für Privatkunden</t>
+  </si>
+  <si>
+    <t>Auswählen &amp; Kaufen &gt; Fahrzeuge vergleichen</t>
+  </si>
+  <si>
+    <t>Fahrzeuge vergleichen</t>
+  </si>
+  <si>
+    <t>/de/bmw-modelle-vergleichen</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/bmw-modelle-vergleichen</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW X Modelle</t>
+  </si>
+  <si>
+    <t>BMW X Modelle</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=x</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=x</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 7er</t>
+  </si>
+  <si>
+    <t>BMW 7er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=7</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=7</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 5er</t>
+  </si>
+  <si>
+    <t>BMW 5er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=5</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=5</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 4er</t>
+  </si>
+  <si>
+    <t>BMW 4er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=4</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=4</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 3er</t>
+  </si>
+  <si>
+    <t>BMW 3er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=3</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=3</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 2er</t>
+  </si>
+  <si>
+    <t>BMW 2er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=2</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=2</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW 1er</t>
+  </si>
+  <si>
+    <t>BMW 1er</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?series=1</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?series=1</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW M Modelle</t>
+  </si>
+  <si>
+    <t>BMW M Modelle</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?bmwM=yes</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?bmwM=yes</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW Limousinen</t>
+  </si>
+  <si>
+    <t>BMW Limousinen</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?category=li</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?category=li</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW Concept Cars</t>
+  </si>
+  <si>
+    <t>BMW Concept Cars</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?specialCategory=c</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?specialCategory=c</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW Exklusive Automobile</t>
+  </si>
+  <si>
+    <t>BMW Exklusive Automobile</t>
+  </si>
+  <si>
+    <t>Modelle &gt; BMW Behörden- und Sonderschutzfahrzeuge</t>
+  </si>
+  <si>
+    <t>BMW Behörden- und Sonderschutzfahrzeuge</t>
+  </si>
+  <si>
+    <t>/de/neufahrzeuge?specialCategory=p</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/neufahrzeuge?specialCategory=p</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; BMW Elektroautos</t>
+  </si>
+  <si>
+    <t>BMW Elektroautos</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; Öffentliches Laden</t>
+  </si>
+  <si>
+    <t>Öffentliches Laden</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; Zuhause Laden</t>
+  </si>
+  <si>
+    <t>Zuhause Laden</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; Reichweite von Elektroautos</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; Kosten eines Elektroautos</t>
+  </si>
+  <si>
+    <t>BMW Elektrofahrzeuge &gt; BMW Plug-in-Hybrid</t>
+  </si>
+  <si>
+    <t>BMW Plug-in-Hybrid</t>
+  </si>
+  <si>
+    <t>BMW YouTube</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/user/BMWDeutschland#_blank</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/user/BMWDeutschland</t>
+  </si>
+  <si>
+    <t>BMW Facebook</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/BMWDeutschland#_blank</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/BMWDeutschland</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/login/?next=https%3A%2F%2Fwww.facebook.com%2FBMWDeutschland</t>
+  </si>
+  <si>
+    <t>BMW Instagram</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bmwdeutschland/#_blank</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bmwdeutschland/</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/accounts/login/?next=https%3A%2F%2Fwww.instagram.com%2Fbmwdeutschland%2F&amp;is_from_rle</t>
+  </si>
+  <si>
+    <t>Barrierefreiheit</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/bmw-barrierefreiheit</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/bmw-barrierefreiheit</t>
+  </si>
+  <si>
+    <t>Impressum</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/legal-notice-pool/imprint</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/legal-notice-pool/imprint</t>
+  </si>
+  <si>
+    <t>Datenschutzrichtlinien</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/data-privacy</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/data-privacy</t>
+  </si>
+  <si>
+    <t>Rechtlicher Hinweis</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/legal-disclaimer-pool/legal-disclaimer</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/legal-disclaimer-pool/legal-disclaimer</t>
+  </si>
+  <si>
+    <t>Cookies</t>
+  </si>
+  <si>
+    <t>/de/footer/footer-section/cookie-policy</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/footer-section/cookie-policy</t>
+  </si>
+  <si>
+    <t>Gesetz über digitale Dienste</t>
+  </si>
+  <si>
+    <t>/de/mehr-bmw/digital-services-act</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/mehr-bmw/digital-services-act</t>
+  </si>
+  <si>
+    <t>Betrugserkennung &amp; Sicherheit</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/bmw-betrugsfaelle</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/bmw-betrugsfaelle</t>
+  </si>
+  <si>
     <t>Produktsicherheitsverordnung</t>
   </si>
   <si>
     <t>/de/footer/metanavigation/legal-disclaimer-pool/Produktsicherheitsverordnung</t>
   </si>
   <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/legal-disclaimer-pool/Produktsicherheitsverordnung</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/legal-disclaimer-pool/produktsicherheitsverordnung</t>
+  </si>
+  <si>
+    <t>EU-Batterieverordnung</t>
+  </si>
+  <si>
+    <t>/de/footer/metanavigation/eu-batterieverordnung</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/footer/metanavigation/eu-batterieverordnung</t>
+  </si>
+  <si>
+    <t>https://ipm.bmw.com/lean-ipm/digitalhub_dcdc/rfcn_bmw_de#_blank</t>
+  </si>
+  <si>
     <t>Sitemap</t>
   </si>
   <si>
     <t>/de/publicPools/sitemap/sitemap</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/publicPools/sitemap/sitemap</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/de/publicpools/sitemap/sitemap</t>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>2026-09-27T18:25:36.678Z</t>
+  </si>
+  <si>
+    <t>Nav source</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/nav.plain.html</t>
+  </si>
+  <si>
+    <t>Footer source</t>
+  </si>
+  <si>
+    <t>https://main--bmw--moved-permanently.aem.page/footer.plain.html</t>
+  </si>
+  <si>
+    <t>Links checked</t>
+  </si>
+  <si>
+    <t>Still pointing to BMW domains</t>
+  </si>
+  <si>
+    <t>Local links dead (404/error)</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>A local link counts as dead only if its final response (after redirects) is 404, 5xx or a network error.</t>
   </si>
 </sst>
 </file>
@@ -902,7 +1905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -911,11 +1914,12 @@
     <col min="4" max="4" width="80" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="9" max="9" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -940,1205 +1944,1346 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3">
-        <v>200</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11">
+        <v>200</v>
+      </c>
+      <c r="F11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12">
+        <v>200</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="s">
+      <c r="H12" t="s">
         <v>20</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4">
-        <v>200</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
-        <v>200</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="I12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13">
+        <v>200</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14">
+        <v>200</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
+        <v>13</v>
+      </c>
+      <c r="I14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15">
+        <v>200</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16">
+        <v>200</v>
+      </c>
+      <c r="F16" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>200</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7">
-        <v>200</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8">
-        <v>200</v>
-      </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17">
+        <v>200</v>
+      </c>
+      <c r="F17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18">
+        <v>200</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19">
+        <v>200</v>
+      </c>
+      <c r="F19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20">
+        <v>200</v>
+      </c>
+      <c r="F20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21">
+        <v>200</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" t="s">
         <v>43</v>
       </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9">
-        <v>200</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10">
-        <v>200</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>200</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H11" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12">
-        <v>200</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13">
-        <v>200</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>200</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15">
-        <v>200</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16">
-        <v>200</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17">
-        <v>200</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18">
-        <v>200</v>
-      </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19">
-        <v>200</v>
-      </c>
-      <c r="F19" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20">
-        <v>200</v>
-      </c>
-      <c r="F20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21">
-        <v>200</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22">
+        <v>200</v>
+      </c>
+      <c r="F22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>89</v>
       </c>
-      <c r="E22">
-        <v>200</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23">
+        <v>200</v>
+      </c>
+      <c r="F23" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>89</v>
       </c>
-      <c r="G22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23">
-        <v>200</v>
-      </c>
-      <c r="F23" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>87</v>
-      </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E24">
         <v>200</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>400</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="H25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E26">
         <v>400</v>
       </c>
       <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
         <v>101</v>
       </c>
-      <c r="G26" t="s">
-        <v>12</v>
-      </c>
       <c r="H26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I26" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E27">
         <v>200</v>
       </c>
       <c r="F27" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E28">
         <v>200</v>
       </c>
       <c r="F28" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H28" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E29">
         <v>200</v>
       </c>
       <c r="F29" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H29" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E30">
         <v>200</v>
       </c>
       <c r="F30" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E31">
         <v>200</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="I31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32">
+        <v>200</v>
+      </c>
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33">
+        <v>200</v>
+      </c>
+      <c r="F33" t="s">
         <v>64</v>
       </c>
-      <c r="D32" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32">
-        <v>200</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>102</v>
-      </c>
-      <c r="B33" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33">
-        <v>200</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
       <c r="G33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E34">
         <v>404</v>
       </c>
       <c r="F34" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E35">
         <v>200</v>
       </c>
       <c r="F35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G35" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H35" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E36">
         <v>200</v>
       </c>
       <c r="F36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H36" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I36" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E37">
         <v>200</v>
       </c>
       <c r="F37" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H37" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" t="s">
+        <v>137</v>
+      </c>
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38">
+        <v>200</v>
+      </c>
+      <c r="F38" t="s">
+        <v>138</v>
+      </c>
+      <c r="G38" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>102</v>
-      </c>
-      <c r="B38" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" t="s">
-        <v>135</v>
-      </c>
-      <c r="D38" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38">
-        <v>200</v>
-      </c>
-      <c r="F38" t="s">
-        <v>136</v>
-      </c>
-      <c r="G38" t="s">
-        <v>12</v>
-      </c>
       <c r="H38" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>105</v>
+      </c>
+      <c r="B39" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" t="s">
+        <v>140</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39">
+        <v>200</v>
+      </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B39" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" t="s">
-        <v>40</v>
-      </c>
-      <c r="E39">
-        <v>200</v>
-      </c>
-      <c r="F39" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" t="s">
-        <v>22</v>
-      </c>
       <c r="H39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I39" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B40" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C40" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E40">
         <v>200</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="D41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E41">
         <v>200</v>
       </c>
       <c r="F41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G41" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C42" t="s">
+        <v>45</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42">
+        <v>200</v>
+      </c>
+      <c r="F42" t="s">
+        <v>46</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
+        <v>13</v>
+      </c>
+      <c r="I42" t="s">
         <v>43</v>
       </c>
-      <c r="D42" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42">
-        <v>200</v>
-      </c>
-      <c r="F42" t="s">
-        <v>44</v>
-      </c>
-      <c r="G42" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43">
         <v>200</v>
       </c>
       <c r="F43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H43" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E44">
         <v>200</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G44" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E45">
         <v>200</v>
       </c>
       <c r="F45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="I45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E46">
         <v>200</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H46" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="I46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E47">
         <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H47" t="s">
-        <v>158</v>
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2146,16 +3291,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="70" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2166,63 +3317,4538 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="E2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="E3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H3">
+        <v>200</v>
+      </c>
+      <c r="I3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4" t="s">
+        <v>179</v>
+      </c>
+      <c r="J4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6">
+        <v>200</v>
+      </c>
+      <c r="I6" t="s">
+        <v>185</v>
+      </c>
+      <c r="J6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7">
+        <v>200</v>
+      </c>
+      <c r="I7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" t="s">
+        <v>176</v>
+      </c>
+      <c r="G8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8">
+        <v>200</v>
+      </c>
+      <c r="I8" t="s">
+        <v>190</v>
+      </c>
+      <c r="J8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9">
+        <v>200</v>
+      </c>
+      <c r="I9" t="s">
+        <v>194</v>
+      </c>
+      <c r="J9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G10" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10">
+        <v>200</v>
+      </c>
+      <c r="I10" t="s">
+        <v>198</v>
+      </c>
+      <c r="J10" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C11" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H11">
+        <v>200</v>
+      </c>
+      <c r="I11" t="s">
+        <v>202</v>
+      </c>
+      <c r="J11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12">
+        <v>200</v>
+      </c>
+      <c r="I12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" t="s">
+        <v>186</v>
+      </c>
+      <c r="G13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13">
+        <v>200</v>
+      </c>
+      <c r="I13" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" t="s">
+        <v>171</v>
+      </c>
+      <c r="H14">
+        <v>200</v>
+      </c>
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" t="s">
+        <v>186</v>
+      </c>
+      <c r="G15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15">
+        <v>200</v>
+      </c>
+      <c r="I15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16">
+        <v>200</v>
+      </c>
+      <c r="I16" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" t="s">
+        <v>206</v>
+      </c>
+      <c r="F17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G17" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17">
+        <v>200</v>
+      </c>
+      <c r="I17" t="s">
+        <v>206</v>
+      </c>
+      <c r="J17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D18" t="s">
+        <v>209</v>
+      </c>
+      <c r="E18" t="s">
+        <v>210</v>
+      </c>
+      <c r="F18" t="s">
+        <v>176</v>
+      </c>
+      <c r="G18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18">
+        <v>200</v>
+      </c>
+      <c r="I18" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C19" t="s">
+        <v>212</v>
+      </c>
+      <c r="D19" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G19" t="s">
+        <v>171</v>
+      </c>
+      <c r="H19">
+        <v>200</v>
+      </c>
+      <c r="I19" t="s">
+        <v>214</v>
+      </c>
+      <c r="J19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" t="s">
+        <v>186</v>
+      </c>
+      <c r="G20" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20">
+        <v>200</v>
+      </c>
+      <c r="I20" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" t="s">
+        <v>186</v>
+      </c>
+      <c r="G21" t="s">
+        <v>171</v>
+      </c>
+      <c r="H21">
+        <v>200</v>
+      </c>
+      <c r="I21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" t="s">
+        <v>186</v>
+      </c>
+      <c r="G22" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22">
+        <v>200</v>
+      </c>
+      <c r="I22" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>217</v>
+      </c>
+      <c r="F23" t="s">
+        <v>176</v>
+      </c>
+      <c r="G23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H23">
+        <v>200</v>
+      </c>
+      <c r="I23" t="s">
+        <v>217</v>
+      </c>
+      <c r="J23" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" t="s">
+        <v>221</v>
+      </c>
+      <c r="F24" t="s">
+        <v>176</v>
+      </c>
+      <c r="G24" t="s">
+        <v>171</v>
+      </c>
+      <c r="H24">
+        <v>200</v>
+      </c>
+      <c r="I24" t="s">
+        <v>221</v>
+      </c>
+      <c r="J24" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E25" t="s">
+        <v>225</v>
+      </c>
+      <c r="F25" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" t="s">
+        <v>171</v>
+      </c>
+      <c r="H25">
+        <v>200</v>
+      </c>
+      <c r="I25" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26" t="s">
+        <v>227</v>
+      </c>
+      <c r="D26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E26" t="s">
+        <v>229</v>
+      </c>
+      <c r="F26" t="s">
+        <v>176</v>
+      </c>
+      <c r="G26" t="s">
+        <v>171</v>
+      </c>
+      <c r="H26">
+        <v>200</v>
+      </c>
+      <c r="I26" t="s">
+        <v>229</v>
+      </c>
+      <c r="J26" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" t="s">
+        <v>231</v>
+      </c>
+      <c r="D27" t="s">
+        <v>232</v>
+      </c>
+      <c r="E27" t="s">
+        <v>233</v>
+      </c>
+      <c r="F27" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27">
+        <v>200</v>
+      </c>
+      <c r="I27" t="s">
+        <v>233</v>
+      </c>
+      <c r="J27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>234</v>
+      </c>
+      <c r="C28" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" t="s">
+        <v>237</v>
+      </c>
+      <c r="F28" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" t="s">
+        <v>238</v>
+      </c>
+      <c r="H28">
+        <v>200</v>
+      </c>
+      <c r="I28" t="s">
+        <v>239</v>
+      </c>
+      <c r="J28" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" t="s">
+        <v>242</v>
+      </c>
+      <c r="E29" t="s">
+        <v>243</v>
+      </c>
+      <c r="F29" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" t="s">
+        <v>171</v>
+      </c>
+      <c r="H29">
+        <v>200</v>
+      </c>
+      <c r="I29" t="s">
+        <v>243</v>
+      </c>
+      <c r="J29" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" t="s">
+        <v>186</v>
+      </c>
+      <c r="G30" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30">
+        <v>200</v>
+      </c>
+      <c r="I30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="s">
+        <v>244</v>
+      </c>
+      <c r="C31" t="s">
+        <v>245</v>
+      </c>
+      <c r="D31" t="s">
+        <v>246</v>
+      </c>
+      <c r="E31" t="s">
+        <v>247</v>
+      </c>
+      <c r="F31" t="s">
+        <v>176</v>
+      </c>
+      <c r="G31" t="s">
+        <v>171</v>
+      </c>
+      <c r="H31">
+        <v>200</v>
+      </c>
+      <c r="I31" t="s">
+        <v>247</v>
+      </c>
+      <c r="J31" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C32" t="s">
+        <v>249</v>
+      </c>
+      <c r="D32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" t="s">
+        <v>251</v>
+      </c>
+      <c r="F32" t="s">
+        <v>176</v>
+      </c>
+      <c r="G32" t="s">
+        <v>171</v>
+      </c>
+      <c r="H32">
+        <v>200</v>
+      </c>
+      <c r="I32" t="s">
+        <v>251</v>
+      </c>
+      <c r="J32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" t="s">
+        <v>252</v>
+      </c>
+      <c r="C33" t="s">
+        <v>253</v>
+      </c>
+      <c r="D33" t="s">
+        <v>254</v>
+      </c>
+      <c r="E33" t="s">
+        <v>255</v>
+      </c>
+      <c r="F33" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33">
+        <v>200</v>
+      </c>
+      <c r="I33" t="s">
+        <v>255</v>
+      </c>
+      <c r="J33" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" t="s">
+        <v>257</v>
+      </c>
+      <c r="D34" t="s">
+        <v>258</v>
+      </c>
+      <c r="E34" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" t="s">
+        <v>176</v>
+      </c>
+      <c r="G34" t="s">
+        <v>171</v>
+      </c>
+      <c r="H34">
+        <v>200</v>
+      </c>
+      <c r="I34" t="s">
+        <v>259</v>
+      </c>
+      <c r="J34" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" t="s">
+        <v>260</v>
+      </c>
+      <c r="C35" t="s">
+        <v>261</v>
+      </c>
+      <c r="D35" t="s">
+        <v>262</v>
+      </c>
+      <c r="E35" t="s">
+        <v>263</v>
+      </c>
+      <c r="F35" t="s">
+        <v>176</v>
+      </c>
+      <c r="G35" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35">
+        <v>200</v>
+      </c>
+      <c r="I35" t="s">
+        <v>264</v>
+      </c>
+      <c r="J35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>265</v>
+      </c>
+      <c r="C36" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E36" t="s">
+        <v>268</v>
+      </c>
+      <c r="F36" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36">
+        <v>200</v>
+      </c>
+      <c r="I36" t="s">
+        <v>268</v>
+      </c>
+      <c r="J36" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" t="s">
+        <v>271</v>
+      </c>
+      <c r="E37" t="s">
+        <v>272</v>
+      </c>
+      <c r="F37" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37">
+        <v>200</v>
+      </c>
+      <c r="I37" t="s">
+        <v>272</v>
+      </c>
+      <c r="J37" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>273</v>
+      </c>
+      <c r="C38" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38">
+        <v>200</v>
+      </c>
+      <c r="I38" t="s">
+        <v>276</v>
+      </c>
+      <c r="J38" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>277</v>
+      </c>
+      <c r="C39" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" t="s">
+        <v>279</v>
+      </c>
+      <c r="E39" t="s">
+        <v>280</v>
+      </c>
+      <c r="F39" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39">
+        <v>200</v>
+      </c>
+      <c r="I39" t="s">
+        <v>280</v>
+      </c>
+      <c r="J39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" t="s">
+        <v>282</v>
+      </c>
+      <c r="D40" t="s">
+        <v>283</v>
+      </c>
+      <c r="E40" t="s">
+        <v>284</v>
+      </c>
+      <c r="F40" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40">
+        <v>200</v>
+      </c>
+      <c r="I40" t="s">
+        <v>284</v>
+      </c>
+      <c r="J40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>285</v>
+      </c>
+      <c r="C41" t="s">
+        <v>286</v>
+      </c>
+      <c r="D41" t="s">
+        <v>287</v>
+      </c>
+      <c r="E41" t="s">
+        <v>288</v>
+      </c>
+      <c r="F41" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41">
+        <v>200</v>
+      </c>
+      <c r="I41" t="s">
+        <v>288</v>
+      </c>
+      <c r="J41" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" t="s">
+        <v>186</v>
+      </c>
+      <c r="G42" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42">
+        <v>200</v>
+      </c>
+      <c r="I42" t="s">
+        <v>57</v>
+      </c>
+      <c r="J42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
+        <v>289</v>
+      </c>
+      <c r="C43" t="s">
+        <v>290</v>
+      </c>
+      <c r="D43" t="s">
+        <v>291</v>
+      </c>
+      <c r="E43" t="s">
+        <v>292</v>
+      </c>
+      <c r="F43" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43">
+        <v>200</v>
+      </c>
+      <c r="I43" t="s">
+        <v>292</v>
+      </c>
+      <c r="J43" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" t="s">
+        <v>294</v>
+      </c>
+      <c r="D44" t="s">
+        <v>295</v>
+      </c>
+      <c r="E44" t="s">
+        <v>296</v>
+      </c>
+      <c r="F44" t="s">
+        <v>176</v>
+      </c>
+      <c r="G44" t="s">
+        <v>171</v>
+      </c>
+      <c r="H44">
+        <v>200</v>
+      </c>
+      <c r="I44" t="s">
+        <v>296</v>
+      </c>
+      <c r="J44" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" t="s">
+        <v>297</v>
+      </c>
+      <c r="C45" t="s">
+        <v>298</v>
+      </c>
+      <c r="D45" t="s">
+        <v>299</v>
+      </c>
+      <c r="E45" t="s">
+        <v>300</v>
+      </c>
+      <c r="F45" t="s">
+        <v>176</v>
+      </c>
+      <c r="G45" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45">
+        <v>200</v>
+      </c>
+      <c r="I45" t="s">
+        <v>300</v>
+      </c>
+      <c r="J45" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" t="s">
+        <v>186</v>
+      </c>
+      <c r="G46" t="s">
+        <v>171</v>
+      </c>
+      <c r="H46">
+        <v>200</v>
+      </c>
+      <c r="I46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" t="s">
+        <v>301</v>
+      </c>
+      <c r="C47" t="s">
+        <v>302</v>
+      </c>
+      <c r="D47" t="s">
+        <v>242</v>
+      </c>
+      <c r="E47" t="s">
+        <v>243</v>
+      </c>
+      <c r="F47" t="s">
+        <v>176</v>
+      </c>
+      <c r="G47" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47">
+        <v>200</v>
+      </c>
+      <c r="I47" t="s">
+        <v>243</v>
+      </c>
+      <c r="J47" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" t="s">
+        <v>303</v>
+      </c>
+      <c r="C48" t="s">
+        <v>304</v>
+      </c>
+      <c r="D48" t="s">
+        <v>305</v>
+      </c>
+      <c r="E48" t="s">
+        <v>306</v>
+      </c>
+      <c r="F48" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48">
+        <v>200</v>
+      </c>
+      <c r="I48" t="s">
+        <v>306</v>
+      </c>
+      <c r="J48" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D49" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" t="s">
+        <v>64</v>
+      </c>
+      <c r="F49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G49" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49">
+        <v>200</v>
+      </c>
+      <c r="I49" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>307</v>
+      </c>
+      <c r="C50" t="s">
+        <v>308</v>
+      </c>
+      <c r="D50" t="s">
+        <v>305</v>
+      </c>
+      <c r="E50" t="s">
+        <v>306</v>
+      </c>
+      <c r="F50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50">
+        <v>200</v>
+      </c>
+      <c r="I50" t="s">
+        <v>306</v>
+      </c>
+      <c r="J50" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" t="s">
+        <v>309</v>
+      </c>
+      <c r="C51" t="s">
+        <v>310</v>
+      </c>
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51" t="s">
+        <v>312</v>
+      </c>
+      <c r="F51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G51" t="s">
+        <v>171</v>
+      </c>
+      <c r="H51">
+        <v>200</v>
+      </c>
+      <c r="I51" t="s">
+        <v>312</v>
+      </c>
+      <c r="J51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" t="s">
+        <v>314</v>
+      </c>
+      <c r="E52" t="s">
+        <v>315</v>
+      </c>
+      <c r="F52" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" t="s">
+        <v>171</v>
+      </c>
+      <c r="H52">
+        <v>200</v>
+      </c>
+      <c r="I52" t="s">
+        <v>315</v>
+      </c>
+      <c r="J52" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" t="s">
+        <v>316</v>
+      </c>
+      <c r="C53" t="s">
+        <v>317</v>
+      </c>
+      <c r="D53" t="s">
+        <v>318</v>
+      </c>
+      <c r="E53" t="s">
+        <v>319</v>
+      </c>
+      <c r="F53" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" t="s">
+        <v>171</v>
+      </c>
+      <c r="H53">
+        <v>200</v>
+      </c>
+      <c r="I53" t="s">
+        <v>319</v>
+      </c>
+      <c r="J53" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" t="s">
+        <v>320</v>
+      </c>
+      <c r="C54" t="s">
+        <v>321</v>
+      </c>
+      <c r="D54" t="s">
+        <v>322</v>
+      </c>
+      <c r="E54" t="s">
+        <v>323</v>
+      </c>
+      <c r="F54" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" t="s">
+        <v>171</v>
+      </c>
+      <c r="H54">
+        <v>200</v>
+      </c>
+      <c r="I54" t="s">
+        <v>323</v>
+      </c>
+      <c r="J54" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D55" t="s">
+        <v>67</v>
+      </c>
+      <c r="E55" t="s">
+        <v>67</v>
+      </c>
+      <c r="F55" t="s">
+        <v>186</v>
+      </c>
+      <c r="G55" t="s">
+        <v>171</v>
+      </c>
+      <c r="H55">
+        <v>200</v>
+      </c>
+      <c r="I55" t="s">
+        <v>67</v>
+      </c>
+      <c r="J55" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" t="s">
+        <v>71</v>
+      </c>
+      <c r="F56" t="s">
+        <v>186</v>
+      </c>
+      <c r="G56" t="s">
+        <v>171</v>
+      </c>
+      <c r="H56">
+        <v>200</v>
+      </c>
+      <c r="I56" t="s">
+        <v>71</v>
+      </c>
+      <c r="J56" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="s">
+        <v>72</v>
+      </c>
+      <c r="C57" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" t="s">
+        <v>186</v>
+      </c>
+      <c r="G57" t="s">
+        <v>171</v>
+      </c>
+      <c r="H57">
+        <v>200</v>
+      </c>
+      <c r="I57" t="s">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" t="s">
+        <v>76</v>
+      </c>
+      <c r="C58" t="s">
+        <v>77</v>
+      </c>
+      <c r="D58" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" t="s">
+        <v>78</v>
+      </c>
+      <c r="F58" t="s">
+        <v>186</v>
+      </c>
+      <c r="G58" t="s">
+        <v>171</v>
+      </c>
+      <c r="H58">
+        <v>200</v>
+      </c>
+      <c r="I58" t="s">
+        <v>78</v>
+      </c>
+      <c r="J58" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D59" t="s">
+        <v>81</v>
+      </c>
+      <c r="E59" t="s">
+        <v>81</v>
+      </c>
+      <c r="F59" t="s">
+        <v>186</v>
+      </c>
+      <c r="G59" t="s">
+        <v>171</v>
+      </c>
+      <c r="H59">
+        <v>200</v>
+      </c>
+      <c r="I59" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" t="s">
+        <v>324</v>
+      </c>
+      <c r="C60" t="s">
+        <v>325</v>
+      </c>
+      <c r="D60" t="s">
+        <v>326</v>
+      </c>
+      <c r="E60" t="s">
+        <v>326</v>
+      </c>
+      <c r="F60" t="s">
+        <v>327</v>
+      </c>
+      <c r="G60" t="s">
+        <v>171</v>
+      </c>
+      <c r="H60">
+        <v>200</v>
+      </c>
+      <c r="I60" t="s">
+        <v>326</v>
+      </c>
+      <c r="J60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" t="s">
+        <v>186</v>
+      </c>
+      <c r="G61" t="s">
+        <v>171</v>
+      </c>
+      <c r="H61">
+        <v>200</v>
+      </c>
+      <c r="I61" t="s">
+        <v>84</v>
+      </c>
+      <c r="J61" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" t="s">
+        <v>328</v>
+      </c>
+      <c r="C62" t="s">
+        <v>329</v>
+      </c>
+      <c r="D62" t="s">
+        <v>330</v>
+      </c>
+      <c r="E62" t="s">
+        <v>331</v>
+      </c>
+      <c r="F62" t="s">
+        <v>176</v>
+      </c>
+      <c r="G62" t="s">
+        <v>171</v>
+      </c>
+      <c r="H62">
+        <v>200</v>
+      </c>
+      <c r="I62" t="s">
+        <v>331</v>
+      </c>
+      <c r="J62" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" t="s">
+        <v>333</v>
+      </c>
+      <c r="D63" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" t="s">
+        <v>335</v>
+      </c>
+      <c r="F63" t="s">
+        <v>176</v>
+      </c>
+      <c r="G63" t="s">
+        <v>171</v>
+      </c>
+      <c r="H63">
+        <v>200</v>
+      </c>
+      <c r="I63" t="s">
+        <v>335</v>
+      </c>
+      <c r="J63" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" t="s">
+        <v>246</v>
+      </c>
+      <c r="E64" t="s">
+        <v>247</v>
+      </c>
+      <c r="F64" t="s">
+        <v>176</v>
+      </c>
+      <c r="G64" t="s">
+        <v>171</v>
+      </c>
+      <c r="H64">
+        <v>200</v>
+      </c>
+      <c r="I64" t="s">
+        <v>247</v>
+      </c>
+      <c r="J64" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" t="s">
+        <v>86</v>
+      </c>
+      <c r="C65" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65" t="s">
+        <v>88</v>
+      </c>
+      <c r="F65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G65" t="s">
+        <v>171</v>
+      </c>
+      <c r="H65">
+        <v>200</v>
+      </c>
+      <c r="I65" t="s">
+        <v>88</v>
+      </c>
+      <c r="J65" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66" t="s">
+        <v>338</v>
+      </c>
+      <c r="C66" t="s">
+        <v>339</v>
+      </c>
+      <c r="D66" t="s">
+        <v>340</v>
+      </c>
+      <c r="E66" t="s">
+        <v>341</v>
+      </c>
+      <c r="F66" t="s">
+        <v>176</v>
+      </c>
+      <c r="G66" t="s">
+        <v>171</v>
+      </c>
+      <c r="H66">
+        <v>200</v>
+      </c>
+      <c r="I66" t="s">
+        <v>341</v>
+      </c>
+      <c r="J66" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" t="s">
+        <v>342</v>
+      </c>
+      <c r="C67" t="s">
+        <v>343</v>
+      </c>
+      <c r="D67" t="s">
+        <v>344</v>
+      </c>
+      <c r="E67" t="s">
+        <v>345</v>
+      </c>
+      <c r="F67" t="s">
+        <v>176</v>
+      </c>
+      <c r="G67" t="s">
+        <v>171</v>
+      </c>
+      <c r="H67">
+        <v>200</v>
+      </c>
+      <c r="I67" t="s">
+        <v>345</v>
+      </c>
+      <c r="J67" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68" t="s">
+        <v>346</v>
+      </c>
+      <c r="C68" t="s">
+        <v>347</v>
+      </c>
+      <c r="D68" t="s">
+        <v>348</v>
+      </c>
+      <c r="E68" t="s">
+        <v>349</v>
+      </c>
+      <c r="F68" t="s">
+        <v>176</v>
+      </c>
+      <c r="G68" t="s">
+        <v>171</v>
+      </c>
+      <c r="H68">
+        <v>200</v>
+      </c>
+      <c r="I68" t="s">
+        <v>349</v>
+      </c>
+      <c r="J68" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" t="s">
+        <v>350</v>
+      </c>
+      <c r="C69" t="s">
+        <v>351</v>
+      </c>
+      <c r="D69" t="s">
+        <v>352</v>
+      </c>
+      <c r="E69" t="s">
+        <v>353</v>
+      </c>
+      <c r="F69" t="s">
+        <v>176</v>
+      </c>
+      <c r="G69" t="s">
+        <v>171</v>
+      </c>
+      <c r="H69">
+        <v>200</v>
+      </c>
+      <c r="I69" t="s">
+        <v>353</v>
+      </c>
+      <c r="J69" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s">
+        <v>354</v>
+      </c>
+      <c r="C70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D70" t="s">
+        <v>356</v>
+      </c>
+      <c r="E70" t="s">
+        <v>357</v>
+      </c>
+      <c r="F70" t="s">
+        <v>176</v>
+      </c>
+      <c r="G70" t="s">
+        <v>171</v>
+      </c>
+      <c r="H70">
+        <v>200</v>
+      </c>
+      <c r="I70" t="s">
+        <v>357</v>
+      </c>
+      <c r="J70" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" t="s">
+        <v>359</v>
+      </c>
+      <c r="D71" t="s">
+        <v>360</v>
+      </c>
+      <c r="E71" t="s">
+        <v>361</v>
+      </c>
+      <c r="F71" t="s">
+        <v>176</v>
+      </c>
+      <c r="G71" t="s">
+        <v>171</v>
+      </c>
+      <c r="H71">
+        <v>200</v>
+      </c>
+      <c r="I71" t="s">
+        <v>361</v>
+      </c>
+      <c r="J71" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" t="s">
+        <v>90</v>
+      </c>
+      <c r="D72" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" t="s">
+        <v>186</v>
+      </c>
+      <c r="G72" t="s">
+        <v>171</v>
+      </c>
+      <c r="H72">
+        <v>200</v>
+      </c>
+      <c r="I72" t="s">
+        <v>91</v>
+      </c>
+      <c r="J72" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73" t="s">
+        <v>92</v>
+      </c>
+      <c r="D73" t="s">
+        <v>93</v>
+      </c>
+      <c r="E73" t="s">
+        <v>93</v>
+      </c>
+      <c r="F73" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73" t="s">
+        <v>171</v>
+      </c>
+      <c r="H73">
+        <v>200</v>
+      </c>
+      <c r="I73" t="s">
+        <v>94</v>
+      </c>
+      <c r="J73" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>89</v>
+      </c>
+      <c r="B74" t="s">
+        <v>95</v>
+      </c>
+      <c r="C74" t="s">
+        <v>95</v>
+      </c>
+      <c r="D74" t="s">
+        <v>96</v>
+      </c>
+      <c r="E74" t="s">
+        <v>96</v>
+      </c>
+      <c r="F74" t="s">
+        <v>186</v>
+      </c>
+      <c r="G74" t="s">
+        <v>171</v>
+      </c>
+      <c r="H74">
+        <v>200</v>
+      </c>
+      <c r="I74" t="s">
+        <v>96</v>
+      </c>
+      <c r="J74" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s">
+        <v>98</v>
+      </c>
+      <c r="C75" t="s">
+        <v>99</v>
+      </c>
+      <c r="D75" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" t="s">
+        <v>100</v>
+      </c>
+      <c r="F75" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" t="s">
+        <v>171</v>
+      </c>
+      <c r="H75">
+        <v>400</v>
+      </c>
+      <c r="I75" t="s">
+        <v>100</v>
+      </c>
+      <c r="J75" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
         <v>102</v>
       </c>
-      <c r="B4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C76" t="s">
+        <v>103</v>
+      </c>
+      <c r="D76" t="s">
+        <v>104</v>
+      </c>
+      <c r="E76" t="s">
+        <v>104</v>
+      </c>
+      <c r="F76" t="s">
+        <v>186</v>
+      </c>
+      <c r="G76" t="s">
+        <v>171</v>
+      </c>
+      <c r="H76">
+        <v>400</v>
+      </c>
+      <c r="I76" t="s">
+        <v>104</v>
+      </c>
+      <c r="J76" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>89</v>
+      </c>
+      <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" t="s">
+        <v>95</v>
+      </c>
+      <c r="D77" t="s">
+        <v>96</v>
+      </c>
+      <c r="E77" t="s">
+        <v>96</v>
+      </c>
+      <c r="F77" t="s">
+        <v>186</v>
+      </c>
+      <c r="G77" t="s">
+        <v>171</v>
+      </c>
+      <c r="H77">
+        <v>200</v>
+      </c>
+      <c r="I77" t="s">
+        <v>96</v>
+      </c>
+      <c r="J77" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>105</v>
+      </c>
+      <c r="B78" t="s">
+        <v>362</v>
+      </c>
+      <c r="C78" t="s">
+        <v>362</v>
+      </c>
+      <c r="D78" t="s">
+        <v>318</v>
+      </c>
+      <c r="E78" t="s">
+        <v>319</v>
+      </c>
+      <c r="F78" t="s">
+        <v>176</v>
+      </c>
+      <c r="G78" t="s">
+        <v>171</v>
+      </c>
+      <c r="H78">
+        <v>200</v>
+      </c>
+      <c r="I78" t="s">
+        <v>319</v>
+      </c>
+      <c r="J78" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>105</v>
+      </c>
+      <c r="B79" t="s">
+        <v>363</v>
+      </c>
+      <c r="C79" t="s">
+        <v>304</v>
+      </c>
+      <c r="D79" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" t="s">
+        <v>306</v>
+      </c>
+      <c r="F79" t="s">
+        <v>176</v>
+      </c>
+      <c r="G79" t="s">
+        <v>171</v>
+      </c>
+      <c r="H79">
+        <v>200</v>
+      </c>
+      <c r="I79" t="s">
+        <v>306</v>
+      </c>
+      <c r="J79" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>105</v>
+      </c>
+      <c r="B80" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" t="s">
+        <v>364</v>
+      </c>
+      <c r="E80" t="s">
+        <v>108</v>
+      </c>
+      <c r="F80" t="s">
+        <v>186</v>
+      </c>
+      <c r="G80" t="s">
+        <v>171</v>
+      </c>
+      <c r="H80">
+        <v>200</v>
+      </c>
+      <c r="I80" t="s">
+        <v>108</v>
+      </c>
+      <c r="J80" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" t="s">
+        <v>110</v>
+      </c>
+      <c r="C81" t="s">
+        <v>111</v>
+      </c>
+      <c r="D81" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" t="s">
+        <v>96</v>
+      </c>
+      <c r="F81" t="s">
+        <v>186</v>
+      </c>
+      <c r="G81" t="s">
+        <v>171</v>
+      </c>
+      <c r="H81">
+        <v>200</v>
+      </c>
+      <c r="I81" t="s">
+        <v>96</v>
+      </c>
+      <c r="J81" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" t="s">
+        <v>365</v>
+      </c>
+      <c r="C82" t="s">
+        <v>366</v>
+      </c>
+      <c r="D82" t="s">
+        <v>367</v>
+      </c>
+      <c r="E82" t="s">
+        <v>368</v>
+      </c>
+      <c r="F82" t="s">
+        <v>176</v>
+      </c>
+      <c r="G82" t="s">
+        <v>171</v>
+      </c>
+      <c r="H82">
+        <v>200</v>
+      </c>
+      <c r="I82" t="s">
+        <v>368</v>
+      </c>
+      <c r="J82" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>105</v>
+      </c>
+      <c r="B83" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" t="s">
+        <v>113</v>
+      </c>
+      <c r="D83" t="s">
+        <v>114</v>
+      </c>
+      <c r="E83" t="s">
+        <v>114</v>
+      </c>
+      <c r="F83" t="s">
+        <v>186</v>
+      </c>
+      <c r="G83" t="s">
+        <v>171</v>
+      </c>
+      <c r="H83">
+        <v>200</v>
+      </c>
+      <c r="I83" t="s">
+        <v>114</v>
+      </c>
+      <c r="J83" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" t="s">
+        <v>116</v>
+      </c>
+      <c r="D84" t="s">
+        <v>74</v>
+      </c>
+      <c r="E84" t="s">
+        <v>74</v>
+      </c>
+      <c r="F84" t="s">
+        <v>186</v>
+      </c>
+      <c r="G84" t="s">
+        <v>171</v>
+      </c>
+      <c r="H84">
+        <v>200</v>
+      </c>
+      <c r="I84" t="s">
+        <v>74</v>
+      </c>
+      <c r="J84" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" t="s">
+        <v>369</v>
+      </c>
+      <c r="C85" t="s">
+        <v>370</v>
+      </c>
+      <c r="D85" t="s">
+        <v>174</v>
+      </c>
+      <c r="E85" t="s">
+        <v>175</v>
+      </c>
+      <c r="F85" t="s">
+        <v>176</v>
+      </c>
+      <c r="G85" t="s">
+        <v>171</v>
+      </c>
+      <c r="H85">
+        <v>200</v>
+      </c>
+      <c r="I85" t="s">
+        <v>175</v>
+      </c>
+      <c r="J85" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>105</v>
+      </c>
+      <c r="B86" t="s">
+        <v>117</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" t="s">
+        <v>67</v>
+      </c>
+      <c r="E86" t="s">
+        <v>67</v>
+      </c>
+      <c r="F86" t="s">
+        <v>186</v>
+      </c>
+      <c r="G86" t="s">
+        <v>171</v>
+      </c>
+      <c r="H86">
+        <v>200</v>
+      </c>
+      <c r="I86" t="s">
+        <v>67</v>
+      </c>
+      <c r="J86" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>105</v>
+      </c>
+      <c r="B87" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" t="s">
+        <v>119</v>
+      </c>
+      <c r="D87" t="s">
+        <v>120</v>
+      </c>
+      <c r="E87" t="s">
+        <v>120</v>
+      </c>
+      <c r="F87" t="s">
+        <v>186</v>
+      </c>
+      <c r="G87" t="s">
+        <v>171</v>
+      </c>
+      <c r="H87">
+        <v>200</v>
+      </c>
+      <c r="I87" t="s">
+        <v>64</v>
+      </c>
+      <c r="J87" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88" t="s">
+        <v>121</v>
+      </c>
+      <c r="C88" t="s">
+        <v>122</v>
+      </c>
+      <c r="D88" t="s">
+        <v>371</v>
+      </c>
+      <c r="E88" t="s">
+        <v>123</v>
+      </c>
+      <c r="F88" t="s">
+        <v>186</v>
+      </c>
+      <c r="G88" t="s">
+        <v>171</v>
+      </c>
+      <c r="H88">
+        <v>404</v>
+      </c>
+      <c r="I88" t="s">
+        <v>123</v>
+      </c>
+      <c r="J88" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" t="s">
+        <v>372</v>
+      </c>
+      <c r="C89" t="s">
+        <v>373</v>
+      </c>
+      <c r="D89" t="s">
+        <v>322</v>
+      </c>
+      <c r="E89" t="s">
+        <v>323</v>
+      </c>
+      <c r="F89" t="s">
+        <v>176</v>
+      </c>
+      <c r="G89" t="s">
+        <v>171</v>
+      </c>
+      <c r="H89">
+        <v>200</v>
+      </c>
+      <c r="I89" t="s">
+        <v>323</v>
+      </c>
+      <c r="J89" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>105</v>
+      </c>
+      <c r="B90" t="s">
+        <v>374</v>
+      </c>
+      <c r="C90" t="s">
+        <v>375</v>
+      </c>
+      <c r="D90" t="s">
+        <v>295</v>
+      </c>
+      <c r="E90" t="s">
+        <v>296</v>
+      </c>
+      <c r="F90" t="s">
+        <v>176</v>
+      </c>
+      <c r="G90" t="s">
+        <v>171</v>
+      </c>
+      <c r="H90">
+        <v>200</v>
+      </c>
+      <c r="I90" t="s">
+        <v>296</v>
+      </c>
+      <c r="J90" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>105</v>
+      </c>
+      <c r="B91" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" t="s">
+        <v>126</v>
+      </c>
+      <c r="D91" t="s">
+        <v>127</v>
+      </c>
+      <c r="E91" t="s">
+        <v>127</v>
+      </c>
+      <c r="F91" t="s">
+        <v>186</v>
+      </c>
+      <c r="G91" t="s">
+        <v>171</v>
+      </c>
+      <c r="H91">
+        <v>200</v>
+      </c>
+      <c r="I91" t="s">
+        <v>127</v>
+      </c>
+      <c r="J91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>105</v>
+      </c>
+      <c r="B92" t="s">
+        <v>376</v>
+      </c>
+      <c r="C92" t="s">
+        <v>377</v>
+      </c>
+      <c r="D92" t="s">
+        <v>322</v>
+      </c>
+      <c r="E92" t="s">
+        <v>323</v>
+      </c>
+      <c r="F92" t="s">
+        <v>176</v>
+      </c>
+      <c r="G92" t="s">
+        <v>171</v>
+      </c>
+      <c r="H92">
+        <v>200</v>
+      </c>
+      <c r="I92" t="s">
+        <v>323</v>
+      </c>
+      <c r="J92" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>105</v>
+      </c>
+      <c r="B93" t="s">
+        <v>128</v>
+      </c>
+      <c r="C93" t="s">
+        <v>129</v>
+      </c>
+      <c r="D93" t="s">
+        <v>378</v>
+      </c>
+      <c r="E93" t="s">
+        <v>130</v>
+      </c>
+      <c r="F93" t="s">
+        <v>186</v>
+      </c>
+      <c r="G93" t="s">
+        <v>171</v>
+      </c>
+      <c r="H93">
+        <v>200</v>
+      </c>
+      <c r="I93" t="s">
+        <v>130</v>
+      </c>
+      <c r="J93" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>105</v>
+      </c>
+      <c r="B94" t="s">
+        <v>379</v>
+      </c>
+      <c r="C94" t="s">
+        <v>183</v>
+      </c>
+      <c r="D94" t="s">
+        <v>184</v>
+      </c>
+      <c r="E94" t="s">
+        <v>185</v>
+      </c>
+      <c r="F94" t="s">
+        <v>176</v>
+      </c>
+      <c r="G94" t="s">
+        <v>171</v>
+      </c>
+      <c r="H94">
+        <v>200</v>
+      </c>
+      <c r="I94" t="s">
+        <v>185</v>
+      </c>
+      <c r="J94" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" t="s">
+        <v>132</v>
+      </c>
+      <c r="C95" t="s">
+        <v>133</v>
+      </c>
+      <c r="D95" t="s">
+        <v>134</v>
+      </c>
+      <c r="E95" t="s">
+        <v>134</v>
+      </c>
+      <c r="F95" t="s">
+        <v>186</v>
+      </c>
+      <c r="G95" t="s">
+        <v>171</v>
+      </c>
+      <c r="H95">
+        <v>200</v>
+      </c>
+      <c r="I95" t="s">
+        <v>135</v>
+      </c>
+      <c r="J95" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>105</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96" t="s">
+        <v>138</v>
+      </c>
+      <c r="E96" t="s">
+        <v>138</v>
+      </c>
+      <c r="F96" t="s">
+        <v>186</v>
+      </c>
+      <c r="G96" t="s">
+        <v>171</v>
+      </c>
+      <c r="H96">
+        <v>200</v>
+      </c>
+      <c r="I96" t="s">
+        <v>138</v>
+      </c>
+      <c r="J96" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" t="s">
+        <v>380</v>
+      </c>
+      <c r="C97" t="s">
+        <v>381</v>
+      </c>
+      <c r="D97" t="s">
+        <v>382</v>
+      </c>
+      <c r="E97" t="s">
+        <v>383</v>
+      </c>
+      <c r="F97" t="s">
+        <v>176</v>
+      </c>
+      <c r="G97" t="s">
+        <v>171</v>
+      </c>
+      <c r="H97">
+        <v>200</v>
+      </c>
+      <c r="I97" t="s">
+        <v>383</v>
+      </c>
+      <c r="J97" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" t="s">
+        <v>139</v>
+      </c>
+      <c r="C98" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" t="s">
+        <v>42</v>
+      </c>
+      <c r="E98" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" t="s">
+        <v>186</v>
+      </c>
+      <c r="G98" t="s">
+        <v>171</v>
+      </c>
+      <c r="H98">
+        <v>200</v>
+      </c>
+      <c r="I98" t="s">
+        <v>42</v>
+      </c>
+      <c r="J98" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" t="s">
+        <v>141</v>
+      </c>
+      <c r="C99" t="s">
+        <v>142</v>
+      </c>
+      <c r="D99" t="s">
+        <v>384</v>
+      </c>
+      <c r="E99" t="s">
+        <v>57</v>
+      </c>
+      <c r="F99" t="s">
+        <v>186</v>
+      </c>
+      <c r="G99" t="s">
+        <v>171</v>
+      </c>
+      <c r="H99">
+        <v>200</v>
+      </c>
+      <c r="I99" t="s">
+        <v>57</v>
+      </c>
+      <c r="J99" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>105</v>
+      </c>
+      <c r="B100" t="s">
+        <v>385</v>
+      </c>
+      <c r="C100" t="s">
+        <v>386</v>
+      </c>
+      <c r="D100" t="s">
+        <v>228</v>
+      </c>
+      <c r="E100" t="s">
+        <v>229</v>
+      </c>
+      <c r="F100" t="s">
+        <v>176</v>
+      </c>
+      <c r="G100" t="s">
+        <v>171</v>
+      </c>
+      <c r="H100">
+        <v>200</v>
+      </c>
+      <c r="I100" t="s">
+        <v>229</v>
+      </c>
+      <c r="J100" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" t="s">
+        <v>143</v>
+      </c>
+      <c r="C101" t="s">
+        <v>92</v>
+      </c>
+      <c r="D101" t="s">
+        <v>93</v>
+      </c>
+      <c r="E101" t="s">
+        <v>93</v>
+      </c>
+      <c r="F101" t="s">
+        <v>186</v>
+      </c>
+      <c r="G101" t="s">
+        <v>171</v>
+      </c>
+      <c r="H101">
+        <v>200</v>
+      </c>
+      <c r="I101" t="s">
+        <v>94</v>
+      </c>
+      <c r="J101" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102" t="s">
+        <v>144</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" t="s">
+        <v>46</v>
+      </c>
+      <c r="E102" t="s">
+        <v>46</v>
+      </c>
+      <c r="F102" t="s">
+        <v>186</v>
+      </c>
+      <c r="G102" t="s">
+        <v>171</v>
+      </c>
+      <c r="H102">
+        <v>200</v>
+      </c>
+      <c r="I102" t="s">
+        <v>46</v>
+      </c>
+      <c r="J102" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" t="s">
+        <v>145</v>
+      </c>
+      <c r="C103" t="s">
+        <v>146</v>
+      </c>
+      <c r="D103" t="s">
+        <v>147</v>
+      </c>
+      <c r="E103" t="s">
+        <v>147</v>
+      </c>
+      <c r="F103" t="s">
+        <v>186</v>
+      </c>
+      <c r="G103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H103">
+        <v>200</v>
+      </c>
+      <c r="I103" t="s">
+        <v>147</v>
+      </c>
+      <c r="J103" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>105</v>
+      </c>
+      <c r="B104" t="s">
+        <v>387</v>
+      </c>
+      <c r="C104" t="s">
+        <v>388</v>
+      </c>
+      <c r="D104" t="s">
+        <v>232</v>
+      </c>
+      <c r="E104" t="s">
+        <v>233</v>
+      </c>
+      <c r="F104" t="s">
+        <v>176</v>
+      </c>
+      <c r="G104" t="s">
+        <v>171</v>
+      </c>
+      <c r="H104">
+        <v>200</v>
+      </c>
+      <c r="I104" t="s">
+        <v>233</v>
+      </c>
+      <c r="J104" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>389</v>
+      </c>
+      <c r="C105" t="s">
+        <v>390</v>
+      </c>
+      <c r="D105" t="s">
+        <v>391</v>
+      </c>
+      <c r="E105" t="s">
+        <v>392</v>
+      </c>
+      <c r="F105" t="s">
+        <v>176</v>
+      </c>
+      <c r="G105" t="s">
+        <v>171</v>
+      </c>
+      <c r="H105">
+        <v>200</v>
+      </c>
+      <c r="I105" t="s">
+        <v>392</v>
+      </c>
+      <c r="J105" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>149</v>
+      </c>
+      <c r="C106" t="s">
+        <v>150</v>
+      </c>
+      <c r="D106" t="s">
+        <v>49</v>
+      </c>
+      <c r="E106" t="s">
+        <v>49</v>
+      </c>
+      <c r="F106" t="s">
+        <v>186</v>
+      </c>
+      <c r="G106" t="s">
+        <v>171</v>
+      </c>
+      <c r="H106">
+        <v>200</v>
+      </c>
+      <c r="I106" t="s">
+        <v>49</v>
+      </c>
+      <c r="J106" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+      <c r="B107" t="s">
+        <v>151</v>
+      </c>
+      <c r="C107" t="s">
+        <v>152</v>
+      </c>
+      <c r="D107" t="s">
+        <v>153</v>
+      </c>
+      <c r="E107" t="s">
+        <v>153</v>
+      </c>
+      <c r="F107" t="s">
+        <v>186</v>
+      </c>
+      <c r="G107" t="s">
+        <v>171</v>
+      </c>
+      <c r="H107">
+        <v>200</v>
+      </c>
+      <c r="I107" t="s">
+        <v>153</v>
+      </c>
+      <c r="J107" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>105</v>
+      </c>
+      <c r="B108" t="s">
+        <v>154</v>
+      </c>
+      <c r="C108" t="s">
+        <v>155</v>
+      </c>
+      <c r="D108" t="s">
+        <v>156</v>
+      </c>
+      <c r="E108" t="s">
+        <v>156</v>
+      </c>
+      <c r="F108" t="s">
+        <v>186</v>
+      </c>
+      <c r="G108" t="s">
+        <v>171</v>
+      </c>
+      <c r="H108">
+        <v>200</v>
+      </c>
+      <c r="I108" t="s">
+        <v>156</v>
+      </c>
+      <c r="J108" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>105</v>
+      </c>
+      <c r="B109" t="s">
+        <v>393</v>
+      </c>
+      <c r="C109" t="s">
+        <v>394</v>
+      </c>
+      <c r="D109" t="s">
+        <v>395</v>
+      </c>
+      <c r="E109" t="s">
+        <v>396</v>
+      </c>
+      <c r="F109" t="s">
+        <v>176</v>
+      </c>
+      <c r="G109" t="s">
+        <v>171</v>
+      </c>
+      <c r="H109">
+        <v>200</v>
+      </c>
+      <c r="I109" t="s">
+        <v>396</v>
+      </c>
+      <c r="J109" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>105</v>
+      </c>
+      <c r="B110" t="s">
+        <v>397</v>
+      </c>
+      <c r="C110" t="s">
+        <v>398</v>
+      </c>
+      <c r="D110" t="s">
+        <v>399</v>
+      </c>
+      <c r="E110" t="s">
+        <v>400</v>
+      </c>
+      <c r="F110" t="s">
+        <v>176</v>
+      </c>
+      <c r="G110" t="s">
+        <v>171</v>
+      </c>
+      <c r="H110">
+        <v>200</v>
+      </c>
+      <c r="I110" t="s">
+        <v>400</v>
+      </c>
+      <c r="J110" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>105</v>
+      </c>
+      <c r="B111" t="s">
+        <v>401</v>
+      </c>
+      <c r="C111" t="s">
+        <v>402</v>
+      </c>
+      <c r="D111" t="s">
+        <v>403</v>
+      </c>
+      <c r="E111" t="s">
+        <v>404</v>
+      </c>
+      <c r="F111" t="s">
+        <v>176</v>
+      </c>
+      <c r="G111" t="s">
+        <v>171</v>
+      </c>
+      <c r="H111">
+        <v>200</v>
+      </c>
+      <c r="I111" t="s">
+        <v>404</v>
+      </c>
+      <c r="J111" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>105</v>
+      </c>
+      <c r="B112" t="s">
+        <v>405</v>
+      </c>
+      <c r="C112" t="s">
+        <v>406</v>
+      </c>
+      <c r="D112" t="s">
+        <v>407</v>
+      </c>
+      <c r="E112" t="s">
+        <v>408</v>
+      </c>
+      <c r="F112" t="s">
+        <v>176</v>
+      </c>
+      <c r="G112" t="s">
+        <v>171</v>
+      </c>
+      <c r="H112">
+        <v>200</v>
+      </c>
+      <c r="I112" t="s">
+        <v>408</v>
+      </c>
+      <c r="J112" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>105</v>
+      </c>
+      <c r="B113" t="s">
+        <v>409</v>
+      </c>
+      <c r="C113" t="s">
+        <v>410</v>
+      </c>
+      <c r="D113" t="s">
+        <v>411</v>
+      </c>
+      <c r="E113" t="s">
+        <v>412</v>
+      </c>
+      <c r="F113" t="s">
+        <v>176</v>
+      </c>
+      <c r="G113" t="s">
+        <v>171</v>
+      </c>
+      <c r="H113">
+        <v>200</v>
+      </c>
+      <c r="I113" t="s">
+        <v>412</v>
+      </c>
+      <c r="J113" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>105</v>
+      </c>
+      <c r="B114" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" t="s">
+        <v>414</v>
+      </c>
+      <c r="D114" t="s">
+        <v>415</v>
+      </c>
+      <c r="E114" t="s">
+        <v>416</v>
+      </c>
+      <c r="F114" t="s">
+        <v>176</v>
+      </c>
+      <c r="G114" t="s">
+        <v>171</v>
+      </c>
+      <c r="H114">
+        <v>200</v>
+      </c>
+      <c r="I114" t="s">
+        <v>416</v>
+      </c>
+      <c r="J114" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>105</v>
+      </c>
+      <c r="B115" t="s">
+        <v>417</v>
+      </c>
+      <c r="C115" t="s">
+        <v>418</v>
+      </c>
+      <c r="D115" t="s">
+        <v>419</v>
+      </c>
+      <c r="E115" t="s">
+        <v>420</v>
+      </c>
+      <c r="F115" t="s">
+        <v>176</v>
+      </c>
+      <c r="G115" t="s">
+        <v>171</v>
+      </c>
+      <c r="H115">
+        <v>200</v>
+      </c>
+      <c r="I115" t="s">
+        <v>420</v>
+      </c>
+      <c r="J115" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>105</v>
+      </c>
+      <c r="B116" t="s">
+        <v>421</v>
+      </c>
+      <c r="C116" t="s">
+        <v>422</v>
+      </c>
+      <c r="D116" t="s">
+        <v>423</v>
+      </c>
+      <c r="E116" t="s">
+        <v>424</v>
+      </c>
+      <c r="F116" t="s">
+        <v>176</v>
+      </c>
+      <c r="G116" t="s">
+        <v>171</v>
+      </c>
+      <c r="H116">
+        <v>200</v>
+      </c>
+      <c r="I116" t="s">
+        <v>424</v>
+      </c>
+      <c r="J116" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>105</v>
+      </c>
+      <c r="B117" t="s">
+        <v>425</v>
+      </c>
+      <c r="C117" t="s">
+        <v>426</v>
+      </c>
+      <c r="D117" t="s">
+        <v>427</v>
+      </c>
+      <c r="E117" t="s">
+        <v>428</v>
+      </c>
+      <c r="F117" t="s">
+        <v>176</v>
+      </c>
+      <c r="G117" t="s">
+        <v>171</v>
+      </c>
+      <c r="H117">
+        <v>200</v>
+      </c>
+      <c r="I117" t="s">
+        <v>428</v>
+      </c>
+      <c r="J117" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>105</v>
+      </c>
+      <c r="B118" t="s">
+        <v>429</v>
+      </c>
+      <c r="C118" t="s">
+        <v>430</v>
+      </c>
+      <c r="D118" t="s">
+        <v>431</v>
+      </c>
+      <c r="E118" t="s">
+        <v>432</v>
+      </c>
+      <c r="F118" t="s">
+        <v>176</v>
+      </c>
+      <c r="G118" t="s">
+        <v>171</v>
+      </c>
+      <c r="H118">
+        <v>200</v>
+      </c>
+      <c r="I118" t="s">
+        <v>432</v>
+      </c>
+      <c r="J118" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>105</v>
+      </c>
+      <c r="B119" t="s">
+        <v>433</v>
+      </c>
+      <c r="C119" t="s">
+        <v>434</v>
+      </c>
+      <c r="D119" t="s">
+        <v>201</v>
+      </c>
+      <c r="E119" t="s">
+        <v>202</v>
+      </c>
+      <c r="F119" t="s">
+        <v>176</v>
+      </c>
+      <c r="G119" t="s">
+        <v>171</v>
+      </c>
+      <c r="H119">
+        <v>200</v>
+      </c>
+      <c r="I119" t="s">
+        <v>202</v>
+      </c>
+      <c r="J119" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>105</v>
+      </c>
+      <c r="B120" t="s">
+        <v>435</v>
+      </c>
+      <c r="C120" t="s">
+        <v>436</v>
+      </c>
+      <c r="D120" t="s">
+        <v>437</v>
+      </c>
+      <c r="E120" t="s">
+        <v>438</v>
+      </c>
+      <c r="F120" t="s">
+        <v>176</v>
+      </c>
+      <c r="G120" t="s">
+        <v>171</v>
+      </c>
+      <c r="H120">
+        <v>200</v>
+      </c>
+      <c r="I120" t="s">
+        <v>438</v>
+      </c>
+      <c r="J120" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>105</v>
+      </c>
+      <c r="B121" t="s">
+        <v>439</v>
+      </c>
+      <c r="C121" t="s">
+        <v>440</v>
+      </c>
+      <c r="D121" t="s">
+        <v>246</v>
+      </c>
+      <c r="E121" t="s">
+        <v>247</v>
+      </c>
+      <c r="F121" t="s">
+        <v>176</v>
+      </c>
+      <c r="G121" t="s">
+        <v>171</v>
+      </c>
+      <c r="H121">
+        <v>200</v>
+      </c>
+      <c r="I121" t="s">
+        <v>247</v>
+      </c>
+      <c r="J121" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>105</v>
+      </c>
+      <c r="B122" t="s">
+        <v>441</v>
+      </c>
+      <c r="C122" t="s">
+        <v>442</v>
+      </c>
+      <c r="D122" t="s">
+        <v>279</v>
+      </c>
+      <c r="E122" t="s">
+        <v>280</v>
+      </c>
+      <c r="F122" t="s">
+        <v>176</v>
+      </c>
+      <c r="G122" t="s">
+        <v>171</v>
+      </c>
+      <c r="H122">
+        <v>200</v>
+      </c>
+      <c r="I122" t="s">
+        <v>280</v>
+      </c>
+      <c r="J122" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>105</v>
+      </c>
+      <c r="B123" t="s">
+        <v>443</v>
+      </c>
+      <c r="C123" t="s">
+        <v>444</v>
+      </c>
+      <c r="D123" t="s">
+        <v>275</v>
+      </c>
+      <c r="E123" t="s">
+        <v>276</v>
+      </c>
+      <c r="F123" t="s">
+        <v>176</v>
+      </c>
+      <c r="G123" t="s">
+        <v>171</v>
+      </c>
+      <c r="H123">
+        <v>200</v>
+      </c>
+      <c r="I123" t="s">
+        <v>276</v>
+      </c>
+      <c r="J123" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>105</v>
+      </c>
+      <c r="B124" t="s">
+        <v>445</v>
+      </c>
+      <c r="C124" t="s">
+        <v>286</v>
+      </c>
+      <c r="D124" t="s">
+        <v>287</v>
+      </c>
+      <c r="E124" t="s">
+        <v>288</v>
+      </c>
+      <c r="F124" t="s">
+        <v>176</v>
+      </c>
+      <c r="G124" t="s">
+        <v>171</v>
+      </c>
+      <c r="H124">
+        <v>200</v>
+      </c>
+      <c r="I124" t="s">
+        <v>288</v>
+      </c>
+      <c r="J124" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>105</v>
+      </c>
+      <c r="B125" t="s">
+        <v>446</v>
+      </c>
+      <c r="C125" t="s">
+        <v>257</v>
+      </c>
+      <c r="D125" t="s">
+        <v>258</v>
+      </c>
+      <c r="E125" t="s">
+        <v>259</v>
+      </c>
+      <c r="F125" t="s">
+        <v>176</v>
+      </c>
+      <c r="G125" t="s">
+        <v>171</v>
+      </c>
+      <c r="H125">
+        <v>200</v>
+      </c>
+      <c r="I125" t="s">
+        <v>259</v>
+      </c>
+      <c r="J125" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>105</v>
+      </c>
+      <c r="B126" t="s">
+        <v>447</v>
+      </c>
+      <c r="C126" t="s">
+        <v>448</v>
+      </c>
+      <c r="D126" t="s">
+        <v>271</v>
+      </c>
+      <c r="E126" t="s">
+        <v>272</v>
+      </c>
+      <c r="F126" t="s">
+        <v>176</v>
+      </c>
+      <c r="G126" t="s">
+        <v>171</v>
+      </c>
+      <c r="H126">
+        <v>200</v>
+      </c>
+      <c r="I126" t="s">
+        <v>272</v>
+      </c>
+      <c r="J126" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>105</v>
+      </c>
+      <c r="B127" t="s">
+        <v>449</v>
+      </c>
+      <c r="C127" t="s">
+        <v>449</v>
+      </c>
+      <c r="D127" t="s">
+        <v>450</v>
+      </c>
+      <c r="E127" t="s">
+        <v>451</v>
+      </c>
+      <c r="F127" t="s">
+        <v>327</v>
+      </c>
+      <c r="G127" t="s">
+        <v>171</v>
+      </c>
+      <c r="H127">
+        <v>200</v>
+      </c>
+      <c r="I127" t="s">
+        <v>451</v>
+      </c>
+      <c r="J127" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>105</v>
+      </c>
+      <c r="B128" t="s">
+        <v>452</v>
+      </c>
+      <c r="C128" t="s">
+        <v>452</v>
+      </c>
+      <c r="D128" t="s">
+        <v>453</v>
+      </c>
+      <c r="E128" t="s">
+        <v>454</v>
+      </c>
+      <c r="F128" t="s">
+        <v>327</v>
+      </c>
+      <c r="G128" t="s">
+        <v>171</v>
+      </c>
+      <c r="H128">
+        <v>400</v>
+      </c>
+      <c r="I128" t="s">
+        <v>455</v>
+      </c>
+      <c r="J128" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" t="s">
+        <v>456</v>
+      </c>
+      <c r="C129" t="s">
+        <v>456</v>
+      </c>
+      <c r="D129" t="s">
+        <v>457</v>
+      </c>
+      <c r="E129" t="s">
+        <v>458</v>
+      </c>
+      <c r="F129" t="s">
+        <v>327</v>
+      </c>
+      <c r="G129" t="s">
+        <v>171</v>
+      </c>
+      <c r="H129">
+        <v>200</v>
+      </c>
+      <c r="I129" t="s">
+        <v>459</v>
+      </c>
+      <c r="J129" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>105</v>
+      </c>
+      <c r="B130" t="s">
+        <v>460</v>
+      </c>
+      <c r="C130" t="s">
+        <v>460</v>
+      </c>
+      <c r="D130" t="s">
+        <v>461</v>
+      </c>
+      <c r="E130" t="s">
+        <v>462</v>
+      </c>
+      <c r="F130" t="s">
+        <v>176</v>
+      </c>
+      <c r="G130" t="s">
+        <v>171</v>
+      </c>
+      <c r="H130">
+        <v>200</v>
+      </c>
+      <c r="I130" t="s">
+        <v>462</v>
+      </c>
+      <c r="J130" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>105</v>
+      </c>
+      <c r="B131" t="s">
+        <v>463</v>
+      </c>
+      <c r="C131" t="s">
+        <v>463</v>
+      </c>
+      <c r="D131" t="s">
+        <v>464</v>
+      </c>
+      <c r="E131" t="s">
+        <v>465</v>
+      </c>
+      <c r="F131" t="s">
+        <v>176</v>
+      </c>
+      <c r="G131" t="s">
+        <v>171</v>
+      </c>
+      <c r="H131">
+        <v>200</v>
+      </c>
+      <c r="I131" t="s">
+        <v>465</v>
+      </c>
+      <c r="J131" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>105</v>
+      </c>
+      <c r="B132" t="s">
+        <v>466</v>
+      </c>
+      <c r="C132" t="s">
+        <v>466</v>
+      </c>
+      <c r="D132" t="s">
+        <v>467</v>
+      </c>
+      <c r="E132" t="s">
+        <v>468</v>
+      </c>
+      <c r="F132" t="s">
+        <v>176</v>
+      </c>
+      <c r="G132" t="s">
+        <v>171</v>
+      </c>
+      <c r="H132">
+        <v>200</v>
+      </c>
+      <c r="I132" t="s">
+        <v>468</v>
+      </c>
+      <c r="J132" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>105</v>
+      </c>
+      <c r="B133" t="s">
+        <v>469</v>
+      </c>
+      <c r="C133" t="s">
+        <v>469</v>
+      </c>
+      <c r="D133" t="s">
+        <v>470</v>
+      </c>
+      <c r="E133" t="s">
+        <v>471</v>
+      </c>
+      <c r="F133" t="s">
+        <v>176</v>
+      </c>
+      <c r="G133" t="s">
+        <v>171</v>
+      </c>
+      <c r="H133">
+        <v>200</v>
+      </c>
+      <c r="I133" t="s">
+        <v>471</v>
+      </c>
+      <c r="J133" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>105</v>
+      </c>
+      <c r="B134" t="s">
+        <v>472</v>
+      </c>
+      <c r="C134" t="s">
+        <v>472</v>
+      </c>
+      <c r="D134" t="s">
+        <v>473</v>
+      </c>
+      <c r="E134" t="s">
+        <v>474</v>
+      </c>
+      <c r="F134" t="s">
+        <v>176</v>
+      </c>
+      <c r="G134" t="s">
+        <v>171</v>
+      </c>
+      <c r="H134">
+        <v>200</v>
+      </c>
+      <c r="I134" t="s">
+        <v>474</v>
+      </c>
+      <c r="J134" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>105</v>
+      </c>
+      <c r="B135" t="s">
+        <v>475</v>
+      </c>
+      <c r="C135" t="s">
+        <v>475</v>
+      </c>
+      <c r="D135" t="s">
+        <v>476</v>
+      </c>
+      <c r="E135" t="s">
+        <v>477</v>
+      </c>
+      <c r="F135" t="s">
+        <v>176</v>
+      </c>
+      <c r="G135" t="s">
+        <v>171</v>
+      </c>
+      <c r="H135">
+        <v>200</v>
+      </c>
+      <c r="I135" t="s">
+        <v>477</v>
+      </c>
+      <c r="J135" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>105</v>
+      </c>
+      <c r="B136" t="s">
+        <v>478</v>
+      </c>
+      <c r="C136" t="s">
+        <v>478</v>
+      </c>
+      <c r="D136" t="s">
+        <v>479</v>
+      </c>
+      <c r="E136" t="s">
+        <v>480</v>
+      </c>
+      <c r="F136" t="s">
+        <v>176</v>
+      </c>
+      <c r="G136" t="s">
+        <v>171</v>
+      </c>
+      <c r="H136">
+        <v>200</v>
+      </c>
+      <c r="I136" t="s">
+        <v>480</v>
+      </c>
+      <c r="J136" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>105</v>
+      </c>
+      <c r="B137" t="s">
+        <v>481</v>
+      </c>
+      <c r="C137" t="s">
+        <v>481</v>
+      </c>
+      <c r="D137" t="s">
+        <v>482</v>
+      </c>
+      <c r="E137" t="s">
+        <v>483</v>
+      </c>
+      <c r="F137" t="s">
+        <v>176</v>
+      </c>
+      <c r="G137" t="s">
+        <v>238</v>
+      </c>
+      <c r="H137">
+        <v>200</v>
+      </c>
+      <c r="I137" t="s">
+        <v>484</v>
+      </c>
+      <c r="J137" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>105</v>
+      </c>
+      <c r="B138" t="s">
+        <v>485</v>
+      </c>
+      <c r="C138" t="s">
+        <v>485</v>
+      </c>
+      <c r="D138" t="s">
+        <v>486</v>
+      </c>
+      <c r="E138" t="s">
+        <v>487</v>
+      </c>
+      <c r="F138" t="s">
+        <v>176</v>
+      </c>
+      <c r="G138" t="s">
+        <v>171</v>
+      </c>
+      <c r="H138">
+        <v>200</v>
+      </c>
+      <c r="I138" t="s">
+        <v>487</v>
+      </c>
+      <c r="J138" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>105</v>
+      </c>
+      <c r="B139" t="s">
+        <v>157</v>
+      </c>
+      <c r="C139" t="s">
+        <v>157</v>
+      </c>
+      <c r="D139" t="s">
+        <v>488</v>
+      </c>
+      <c r="E139" t="s">
+        <v>158</v>
+      </c>
+      <c r="F139" t="s">
+        <v>186</v>
+      </c>
+      <c r="G139" t="s">
+        <v>171</v>
+      </c>
+      <c r="H139">
+        <v>200</v>
+      </c>
+      <c r="I139" t="s">
+        <v>158</v>
+      </c>
+      <c r="J139" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>105</v>
+      </c>
+      <c r="B140" t="s">
+        <v>489</v>
+      </c>
+      <c r="C140" t="s">
+        <v>489</v>
+      </c>
+      <c r="D140" t="s">
+        <v>490</v>
+      </c>
+      <c r="E140" t="s">
+        <v>491</v>
+      </c>
+      <c r="F140" t="s">
+        <v>176</v>
+      </c>
+      <c r="G140" t="s">
+        <v>238</v>
+      </c>
+      <c r="H140">
+        <v>200</v>
+      </c>
+      <c r="I140" t="s">
+        <v>492</v>
+      </c>
+      <c r="J140" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B4">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" t="s">
-        <v>169</v>
+        <v>500</v>
+      </c>
+      <c r="B5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>502</v>
+      </c>
+      <c r="B7" t="s">
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/tools/reports/nav-unmigrated.xlsx
+++ b/tools/reports/nav-unmigrated.xlsx
@@ -1497,7 +1497,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-27T18:25:36.678Z</t>
+    <t>2026-09-28T02:40:56.536Z</t>
   </si>
   <si>
     <t>Nav source</t>
